--- a/data_lake/macro/South Korea/M2.xlsx
+++ b/data_lake/macro/South Korea/M2.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\South Korea\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/macro/South Korea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D1B189-CE3B-4927-ABC6-290244157285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16DBFE93-5860-4C41-831F-F91D1905D94C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{08BCB5FB-51DD-450F-BCB2-E76A200295D9}"/>
+    <workbookView xWindow="14920" yWindow="780" windowWidth="23260" windowHeight="12460" activeTab="1" xr2:uid="{08BCB5FB-51DD-450F-BCB2-E76A200295D9}"/>
   </bookViews>
   <sheets>
     <sheet name="KOM2Y" sheetId="1" r:id="rId1"/>
+    <sheet name="info" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="18">
   <si>
     <t>Release Date</t>
   </si>
@@ -59,6 +60,44 @@
   <si>
     <t>UTC+9</t>
   </si>
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ticker</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>URL</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Frequency</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exchange</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Country</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monthly</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>South Korea</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOM2Y</t>
+  </si>
+  <si>
+    <t>https://kr.investing.com/economic-calendar/south-korean-m2-money-supply-787</t>
+  </si>
 </sst>
 </file>
 
@@ -68,7 +107,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,16 +121,37 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -99,11 +159,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -128,9 +204,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -146,9 +235,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -186,7 +275,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -292,7 +381,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -434,7 +523,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -442,16 +531,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09608594-E95B-400F-8DBA-543E2A2BA937}">
-  <dimension ref="A1:H367"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H369"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>6</v>
       </c>
@@ -475,9 +564,9 @@
       </c>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
-        <v>35065</v>
+        <v>35034</v>
       </c>
       <c r="B2" s="4">
         <v>35096</v>
@@ -494,9 +583,9 @@
       <c r="G2" s="1"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
-        <v>35096</v>
+        <v>35065</v>
       </c>
       <c r="B3" s="4">
         <v>35125</v>
@@ -515,9 +604,9 @@
       </c>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
-        <v>35125</v>
+        <v>35096</v>
       </c>
       <c r="B4" s="4">
         <v>35156</v>
@@ -536,9 +625,9 @@
       </c>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
-        <v>35156</v>
+        <v>35125</v>
       </c>
       <c r="B5" s="4">
         <v>35186</v>
@@ -557,9 +646,9 @@
       </c>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
-        <v>35186</v>
+        <v>35156</v>
       </c>
       <c r="B6" s="4">
         <v>35217</v>
@@ -578,9 +667,9 @@
       </c>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
-        <v>35217</v>
+        <v>35186</v>
       </c>
       <c r="B7" s="4">
         <v>35247</v>
@@ -599,9 +688,9 @@
       </c>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
-        <v>35247</v>
+        <v>35217</v>
       </c>
       <c r="B8" s="4">
         <v>35278</v>
@@ -620,9 +709,9 @@
       </c>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
-        <v>35278</v>
+        <v>35247</v>
       </c>
       <c r="B9" s="4">
         <v>35309</v>
@@ -641,9 +730,9 @@
       </c>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
-        <v>35309</v>
+        <v>35278</v>
       </c>
       <c r="B10" s="4">
         <v>35339</v>
@@ -662,9 +751,9 @@
       </c>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
-        <v>35339</v>
+        <v>35309</v>
       </c>
       <c r="B11" s="4">
         <v>35370</v>
@@ -683,9 +772,9 @@
       </c>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
-        <v>35370</v>
+        <v>35339</v>
       </c>
       <c r="B12" s="4">
         <v>35400</v>
@@ -704,9 +793,9 @@
       </c>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>35400</v>
+        <v>35370</v>
       </c>
       <c r="B13" s="4">
         <v>35431</v>
@@ -725,9 +814,9 @@
       </c>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
-        <v>35431</v>
+        <v>35400</v>
       </c>
       <c r="B14" s="4">
         <v>35462</v>
@@ -746,9 +835,9 @@
       </c>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
-        <v>35462</v>
+        <v>35431</v>
       </c>
       <c r="B15" s="4">
         <v>35490</v>
@@ -767,9 +856,9 @@
       </c>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
-        <v>35490</v>
+        <v>35462</v>
       </c>
       <c r="B16" s="4">
         <v>35521</v>
@@ -788,9 +877,9 @@
       </c>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
-        <v>35521</v>
+        <v>35490</v>
       </c>
       <c r="B17" s="4">
         <v>35551</v>
@@ -809,9 +898,9 @@
       </c>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
-        <v>35551</v>
+        <v>35521</v>
       </c>
       <c r="B18" s="4">
         <v>35582</v>
@@ -830,9 +919,9 @@
       </c>
       <c r="H18" s="2"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
-        <v>35582</v>
+        <v>35551</v>
       </c>
       <c r="B19" s="4">
         <v>35612</v>
@@ -851,9 +940,9 @@
       </c>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
-        <v>35612</v>
+        <v>35582</v>
       </c>
       <c r="B20" s="4">
         <v>35643</v>
@@ -872,9 +961,9 @@
       </c>
       <c r="H20" s="2"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
-        <v>35643</v>
+        <v>35612</v>
       </c>
       <c r="B21" s="4">
         <v>35674</v>
@@ -893,9 +982,9 @@
       </c>
       <c r="H21" s="2"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
-        <v>35674</v>
+        <v>35643</v>
       </c>
       <c r="B22" s="4">
         <v>35704</v>
@@ -914,9 +1003,9 @@
       </c>
       <c r="H22" s="2"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
-        <v>35704</v>
+        <v>35674</v>
       </c>
       <c r="B23" s="4">
         <v>35735</v>
@@ -935,9 +1024,9 @@
       </c>
       <c r="H23" s="2"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>35735</v>
+        <v>35704</v>
       </c>
       <c r="B24" s="4">
         <v>35765</v>
@@ -956,9 +1045,9 @@
       </c>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
-        <v>35765</v>
+        <v>35735</v>
       </c>
       <c r="B25" s="4">
         <v>35796</v>
@@ -977,9 +1066,9 @@
       </c>
       <c r="H25" s="2"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
-        <v>35796</v>
+        <v>35765</v>
       </c>
       <c r="B26" s="4">
         <v>35827</v>
@@ -998,9 +1087,9 @@
       </c>
       <c r="H26" s="2"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
-        <v>35827</v>
+        <v>35796</v>
       </c>
       <c r="B27" s="4">
         <v>35855</v>
@@ -1019,9 +1108,9 @@
       </c>
       <c r="H27" s="2"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
-        <v>35855</v>
+        <v>35827</v>
       </c>
       <c r="B28" s="4">
         <v>35886</v>
@@ -1040,9 +1129,9 @@
       </c>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
-        <v>35886</v>
+        <v>35855</v>
       </c>
       <c r="B29" s="4">
         <v>35916</v>
@@ -1061,9 +1150,9 @@
       </c>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
-        <v>35916</v>
+        <v>35886</v>
       </c>
       <c r="B30" s="4">
         <v>35947</v>
@@ -1082,9 +1171,9 @@
       </c>
       <c r="H30" s="2"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
-        <v>35947</v>
+        <v>35916</v>
       </c>
       <c r="B31" s="4">
         <v>35977</v>
@@ -1103,9 +1192,9 @@
       </c>
       <c r="H31" s="2"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
-        <v>35977</v>
+        <v>35947</v>
       </c>
       <c r="B32" s="4">
         <v>36008</v>
@@ -1124,9 +1213,9 @@
       </c>
       <c r="H32" s="2"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
-        <v>36008</v>
+        <v>35977</v>
       </c>
       <c r="B33" s="4">
         <v>36039</v>
@@ -1145,9 +1234,9 @@
       </c>
       <c r="H33" s="2"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
-        <v>36039</v>
+        <v>36008</v>
       </c>
       <c r="B34" s="4">
         <v>36069</v>
@@ -1166,9 +1255,9 @@
       </c>
       <c r="H34" s="2"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>36069</v>
+        <v>36039</v>
       </c>
       <c r="B35" s="4">
         <v>36100</v>
@@ -1187,9 +1276,9 @@
       </c>
       <c r="H35" s="2"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
-        <v>36100</v>
+        <v>36069</v>
       </c>
       <c r="B36" s="4">
         <v>36130</v>
@@ -1208,9 +1297,9 @@
       </c>
       <c r="H36" s="2"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
-        <v>36130</v>
+        <v>36100</v>
       </c>
       <c r="B37" s="4">
         <v>36161</v>
@@ -1229,9 +1318,9 @@
       </c>
       <c r="H37" s="2"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
-        <v>36161</v>
+        <v>36130</v>
       </c>
       <c r="B38" s="4">
         <v>36192</v>
@@ -1250,9 +1339,9 @@
       </c>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
-        <v>36192</v>
+        <v>36161</v>
       </c>
       <c r="B39" s="4">
         <v>36220</v>
@@ -1271,9 +1360,9 @@
       </c>
       <c r="H39" s="2"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
-        <v>36220</v>
+        <v>36192</v>
       </c>
       <c r="B40" s="4">
         <v>36251</v>
@@ -1292,9 +1381,9 @@
       </c>
       <c r="H40" s="2"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
-        <v>36251</v>
+        <v>36220</v>
       </c>
       <c r="B41" s="4">
         <v>36281</v>
@@ -1313,9 +1402,9 @@
       </c>
       <c r="H41" s="2"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
-        <v>36281</v>
+        <v>36251</v>
       </c>
       <c r="B42" s="4">
         <v>36312</v>
@@ -1334,9 +1423,9 @@
       </c>
       <c r="H42" s="2"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
-        <v>36312</v>
+        <v>36281</v>
       </c>
       <c r="B43" s="4">
         <v>36342</v>
@@ -1355,9 +1444,9 @@
       </c>
       <c r="H43" s="2"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
-        <v>36342</v>
+        <v>36312</v>
       </c>
       <c r="B44" s="4">
         <v>36373</v>
@@ -1376,9 +1465,9 @@
       </c>
       <c r="H44" s="2"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
-        <v>36373</v>
+        <v>36342</v>
       </c>
       <c r="B45" s="4">
         <v>36404</v>
@@ -1397,9 +1486,9 @@
       </c>
       <c r="H45" s="2"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>36404</v>
+        <v>36373</v>
       </c>
       <c r="B46" s="4">
         <v>36434</v>
@@ -1418,9 +1507,9 @@
       </c>
       <c r="H46" s="2"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
-        <v>36434</v>
+        <v>36404</v>
       </c>
       <c r="B47" s="4">
         <v>36465</v>
@@ -1439,9 +1528,9 @@
       </c>
       <c r="H47" s="2"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
-        <v>36465</v>
+        <v>36434</v>
       </c>
       <c r="B48" s="4">
         <v>36495</v>
@@ -1460,9 +1549,9 @@
       </c>
       <c r="H48" s="2"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
-        <v>36495</v>
+        <v>36465</v>
       </c>
       <c r="B49" s="4">
         <v>36526</v>
@@ -1481,9 +1570,9 @@
       </c>
       <c r="H49" s="2"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
-        <v>36526</v>
+        <v>36495</v>
       </c>
       <c r="B50" s="4">
         <v>36557</v>
@@ -1502,9 +1591,9 @@
       </c>
       <c r="H50" s="2"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
-        <v>36557</v>
+        <v>36526</v>
       </c>
       <c r="B51" s="4">
         <v>36586</v>
@@ -1523,9 +1612,9 @@
       </c>
       <c r="H51" s="2"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
-        <v>36586</v>
+        <v>36557</v>
       </c>
       <c r="B52" s="4">
         <v>36617</v>
@@ -1544,9 +1633,9 @@
       </c>
       <c r="H52" s="2"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
-        <v>36617</v>
+        <v>36586</v>
       </c>
       <c r="B53" s="4">
         <v>36647</v>
@@ -1565,9 +1654,9 @@
       </c>
       <c r="H53" s="2"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
-        <v>36647</v>
+        <v>36617</v>
       </c>
       <c r="B54" s="4">
         <v>36678</v>
@@ -1586,9 +1675,9 @@
       </c>
       <c r="H54" s="2"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
-        <v>36678</v>
+        <v>36647</v>
       </c>
       <c r="B55" s="4">
         <v>36708</v>
@@ -1607,9 +1696,9 @@
       </c>
       <c r="H55" s="2"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
-        <v>36708</v>
+        <v>36678</v>
       </c>
       <c r="B56" s="4">
         <v>36739</v>
@@ -1628,9 +1717,9 @@
       </c>
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>36739</v>
+        <v>36708</v>
       </c>
       <c r="B57" s="4">
         <v>36770</v>
@@ -1649,9 +1738,9 @@
       </c>
       <c r="H57" s="2"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
-        <v>36770</v>
+        <v>36739</v>
       </c>
       <c r="B58" s="4">
         <v>36800</v>
@@ -1670,9 +1759,9 @@
       </c>
       <c r="H58" s="2"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
-        <v>36800</v>
+        <v>36770</v>
       </c>
       <c r="B59" s="4">
         <v>36831</v>
@@ -1691,9 +1780,9 @@
       </c>
       <c r="H59" s="2"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
-        <v>36831</v>
+        <v>36800</v>
       </c>
       <c r="B60" s="4">
         <v>36861</v>
@@ -1712,9 +1801,9 @@
       </c>
       <c r="H60" s="2"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
-        <v>36861</v>
+        <v>36831</v>
       </c>
       <c r="B61" s="4">
         <v>36892</v>
@@ -1733,9 +1822,9 @@
       </c>
       <c r="H61" s="2"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
-        <v>36892</v>
+        <v>36861</v>
       </c>
       <c r="B62" s="4">
         <v>36923</v>
@@ -1754,9 +1843,9 @@
       </c>
       <c r="H62" s="2"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
-        <v>36923</v>
+        <v>36892</v>
       </c>
       <c r="B63" s="4">
         <v>36951</v>
@@ -1775,9 +1864,9 @@
       </c>
       <c r="H63" s="2"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
-        <v>36951</v>
+        <v>36923</v>
       </c>
       <c r="B64" s="4">
         <v>36982</v>
@@ -1796,9 +1885,9 @@
       </c>
       <c r="H64" s="2"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
-        <v>36982</v>
+        <v>36951</v>
       </c>
       <c r="B65" s="4">
         <v>37012</v>
@@ -1817,9 +1906,9 @@
       </c>
       <c r="H65" s="2"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
-        <v>37012</v>
+        <v>36982</v>
       </c>
       <c r="B66" s="4">
         <v>37043</v>
@@ -1838,9 +1927,9 @@
       </c>
       <c r="H66" s="2"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
-        <v>37043</v>
+        <v>37012</v>
       </c>
       <c r="B67" s="4">
         <v>37073</v>
@@ -1859,9 +1948,9 @@
       </c>
       <c r="H67" s="2"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>37073</v>
+        <v>37043</v>
       </c>
       <c r="B68" s="4">
         <v>37104</v>
@@ -1880,9 +1969,9 @@
       </c>
       <c r="H68" s="2"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
-        <v>37104</v>
+        <v>37073</v>
       </c>
       <c r="B69" s="4">
         <v>37135</v>
@@ -1901,9 +1990,9 @@
       </c>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
-        <v>37135</v>
+        <v>37104</v>
       </c>
       <c r="B70" s="4">
         <v>37165</v>
@@ -1922,9 +2011,9 @@
       </c>
       <c r="H70" s="2"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
-        <v>37165</v>
+        <v>37135</v>
       </c>
       <c r="B71" s="4">
         <v>37196</v>
@@ -1943,9 +2032,9 @@
       </c>
       <c r="H71" s="2"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
-        <v>37196</v>
+        <v>37165</v>
       </c>
       <c r="B72" s="4">
         <v>37226</v>
@@ -1964,9 +2053,9 @@
       </c>
       <c r="H72" s="2"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
-        <v>37226</v>
+        <v>37196</v>
       </c>
       <c r="B73" s="4">
         <v>37257</v>
@@ -1985,9 +2074,9 @@
       </c>
       <c r="H73" s="2"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
-        <v>37257</v>
+        <v>37226</v>
       </c>
       <c r="B74" s="4">
         <v>37288</v>
@@ -2006,9 +2095,9 @@
       </c>
       <c r="H74" s="2"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
-        <v>37288</v>
+        <v>37257</v>
       </c>
       <c r="B75" s="4">
         <v>37316</v>
@@ -2027,9 +2116,9 @@
       </c>
       <c r="H75" s="2"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
-        <v>37316</v>
+        <v>37288</v>
       </c>
       <c r="B76" s="4">
         <v>37347</v>
@@ -2048,9 +2137,9 @@
       </c>
       <c r="H76" s="2"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
-        <v>37347</v>
+        <v>37316</v>
       </c>
       <c r="B77" s="4">
         <v>37377</v>
@@ -2069,9 +2158,9 @@
       </c>
       <c r="H77" s="2"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
-        <v>37377</v>
+        <v>37347</v>
       </c>
       <c r="B78" s="4">
         <v>37408</v>
@@ -2090,9 +2179,9 @@
       </c>
       <c r="H78" s="2"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>37408</v>
+        <v>37377</v>
       </c>
       <c r="B79" s="4">
         <v>37438</v>
@@ -2111,9 +2200,9 @@
       </c>
       <c r="H79" s="2"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
-        <v>37438</v>
+        <v>37408</v>
       </c>
       <c r="B80" s="4">
         <v>37469</v>
@@ -2132,9 +2221,9 @@
       </c>
       <c r="H80" s="2"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
-        <v>37469</v>
+        <v>37438</v>
       </c>
       <c r="B81" s="4">
         <v>37500</v>
@@ -2153,9 +2242,9 @@
       </c>
       <c r="H81" s="2"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="4">
-        <v>37500</v>
+        <v>37469</v>
       </c>
       <c r="B82" s="4">
         <v>37530</v>
@@ -2174,9 +2263,9 @@
       </c>
       <c r="H82" s="2"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="4">
-        <v>37530</v>
+        <v>37500</v>
       </c>
       <c r="B83" s="4">
         <v>37561</v>
@@ -2195,9 +2284,9 @@
       </c>
       <c r="H83" s="2"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
-        <v>37561</v>
+        <v>37530</v>
       </c>
       <c r="B84" s="4">
         <v>37591</v>
@@ -2216,9 +2305,9 @@
       </c>
       <c r="H84" s="2"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
-        <v>37591</v>
+        <v>37561</v>
       </c>
       <c r="B85" s="4">
         <v>37622</v>
@@ -2237,9 +2326,9 @@
       </c>
       <c r="H85" s="2"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="4">
-        <v>37622</v>
+        <v>37591</v>
       </c>
       <c r="B86" s="4">
         <v>37653</v>
@@ -2258,9 +2347,9 @@
       </c>
       <c r="H86" s="2"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="4">
-        <v>37653</v>
+        <v>37622</v>
       </c>
       <c r="B87" s="4">
         <v>37681</v>
@@ -2279,9 +2368,9 @@
       </c>
       <c r="H87" s="2"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="4">
-        <v>37681</v>
+        <v>37653</v>
       </c>
       <c r="B88" s="4">
         <v>37712</v>
@@ -2300,9 +2389,9 @@
       </c>
       <c r="H88" s="2"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="4">
-        <v>37712</v>
+        <v>37681</v>
       </c>
       <c r="B89" s="4">
         <v>37742</v>
@@ -2321,9 +2410,9 @@
       </c>
       <c r="H89" s="2"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>37742</v>
+        <v>37712</v>
       </c>
       <c r="B90" s="4">
         <v>37773</v>
@@ -2342,9 +2431,9 @@
       </c>
       <c r="H90" s="2"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="4">
-        <v>37773</v>
+        <v>37742</v>
       </c>
       <c r="B91" s="4">
         <v>37803</v>
@@ -2363,9 +2452,9 @@
       </c>
       <c r="H91" s="2"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="4">
-        <v>37803</v>
+        <v>37773</v>
       </c>
       <c r="B92" s="4">
         <v>37834</v>
@@ -2384,9 +2473,9 @@
       </c>
       <c r="H92" s="2"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="4">
-        <v>37834</v>
+        <v>37803</v>
       </c>
       <c r="B93" s="4">
         <v>37865</v>
@@ -2405,9 +2494,9 @@
       </c>
       <c r="H93" s="2"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="4">
-        <v>37865</v>
+        <v>37834</v>
       </c>
       <c r="B94" s="4">
         <v>37895</v>
@@ -2426,9 +2515,9 @@
       </c>
       <c r="H94" s="2"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="4">
-        <v>37895</v>
+        <v>37865</v>
       </c>
       <c r="B95" s="4">
         <v>37926</v>
@@ -2447,9 +2536,9 @@
       </c>
       <c r="H95" s="2"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="4">
-        <v>37926</v>
+        <v>37895</v>
       </c>
       <c r="B96" s="4">
         <v>37956</v>
@@ -2468,9 +2557,9 @@
       </c>
       <c r="H96" s="2"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="4">
-        <v>37956</v>
+        <v>37926</v>
       </c>
       <c r="B97" s="4">
         <v>37987</v>
@@ -2489,9 +2578,9 @@
       </c>
       <c r="H97" s="2"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="4">
-        <v>37987</v>
+        <v>37956</v>
       </c>
       <c r="B98" s="4">
         <v>38018</v>
@@ -2510,9 +2599,9 @@
       </c>
       <c r="H98" s="2"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="4">
-        <v>38018</v>
+        <v>37987</v>
       </c>
       <c r="B99" s="4">
         <v>38047</v>
@@ -2531,9 +2620,9 @@
       </c>
       <c r="H99" s="2"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="4">
-        <v>38047</v>
+        <v>38018</v>
       </c>
       <c r="B100" s="4">
         <v>38078</v>
@@ -2552,9 +2641,9 @@
       </c>
       <c r="H100" s="2"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>38078</v>
+        <v>38047</v>
       </c>
       <c r="B101" s="4">
         <v>38108</v>
@@ -2573,9 +2662,9 @@
       </c>
       <c r="H101" s="2"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="4">
-        <v>38108</v>
+        <v>38078</v>
       </c>
       <c r="B102" s="4">
         <v>38139</v>
@@ -2594,9 +2683,9 @@
       </c>
       <c r="H102" s="2"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="4">
-        <v>38139</v>
+        <v>38108</v>
       </c>
       <c r="B103" s="4">
         <v>38169</v>
@@ -2615,9 +2704,9 @@
       </c>
       <c r="H103" s="2"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="4">
-        <v>38169</v>
+        <v>38139</v>
       </c>
       <c r="B104" s="4">
         <v>38200</v>
@@ -2636,9 +2725,9 @@
       </c>
       <c r="H104" s="2"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="4">
-        <v>38200</v>
+        <v>38169</v>
       </c>
       <c r="B105" s="4">
         <v>38231</v>
@@ -2657,9 +2746,9 @@
       </c>
       <c r="H105" s="2"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="4">
-        <v>38231</v>
+        <v>38200</v>
       </c>
       <c r="B106" s="4">
         <v>38261</v>
@@ -2678,9 +2767,9 @@
       </c>
       <c r="H106" s="2"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="4">
-        <v>38261</v>
+        <v>38231</v>
       </c>
       <c r="B107" s="4">
         <v>38292</v>
@@ -2699,9 +2788,9 @@
       </c>
       <c r="H107" s="2"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="4">
-        <v>38292</v>
+        <v>38261</v>
       </c>
       <c r="B108" s="4">
         <v>38322</v>
@@ -2720,9 +2809,9 @@
       </c>
       <c r="H108" s="2"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="4">
-        <v>38322</v>
+        <v>38292</v>
       </c>
       <c r="B109" s="4">
         <v>38353</v>
@@ -2741,9 +2830,9 @@
       </c>
       <c r="H109" s="2"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="4">
-        <v>38353</v>
+        <v>38322</v>
       </c>
       <c r="B110" s="4">
         <v>38384</v>
@@ -2762,9 +2851,9 @@
       </c>
       <c r="H110" s="2"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="4">
-        <v>38384</v>
+        <v>38353</v>
       </c>
       <c r="B111" s="4">
         <v>38412</v>
@@ -2783,9 +2872,9 @@
       </c>
       <c r="H111" s="2"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>38412</v>
+        <v>38384</v>
       </c>
       <c r="B112" s="4">
         <v>38443</v>
@@ -2804,9 +2893,9 @@
       </c>
       <c r="H112" s="2"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="4">
-        <v>38443</v>
+        <v>38412</v>
       </c>
       <c r="B113" s="4">
         <v>38473</v>
@@ -2825,9 +2914,9 @@
       </c>
       <c r="H113" s="2"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="4">
-        <v>38473</v>
+        <v>38443</v>
       </c>
       <c r="B114" s="4">
         <v>38504</v>
@@ -2846,9 +2935,9 @@
       </c>
       <c r="H114" s="2"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="4">
-        <v>38504</v>
+        <v>38473</v>
       </c>
       <c r="B115" s="4">
         <v>38534</v>
@@ -2867,9 +2956,9 @@
       </c>
       <c r="H115" s="2"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="4">
-        <v>38534</v>
+        <v>38504</v>
       </c>
       <c r="B116" s="4">
         <v>38565</v>
@@ -2888,9 +2977,9 @@
       </c>
       <c r="H116" s="2"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="4">
-        <v>38565</v>
+        <v>38534</v>
       </c>
       <c r="B117" s="4">
         <v>38596</v>
@@ -2909,9 +2998,9 @@
       </c>
       <c r="H117" s="2"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="4">
-        <v>38596</v>
+        <v>38565</v>
       </c>
       <c r="B118" s="4">
         <v>38626</v>
@@ -2930,9 +3019,9 @@
       </c>
       <c r="H118" s="2"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="4">
-        <v>38626</v>
+        <v>38596</v>
       </c>
       <c r="B119" s="4">
         <v>38657</v>
@@ -2951,9 +3040,9 @@
       </c>
       <c r="H119" s="2"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="4">
-        <v>38657</v>
+        <v>38626</v>
       </c>
       <c r="B120" s="4">
         <v>38687</v>
@@ -2972,9 +3061,9 @@
       </c>
       <c r="H120" s="2"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="4">
-        <v>38687</v>
+        <v>38657</v>
       </c>
       <c r="B121" s="4">
         <v>38718</v>
@@ -2993,9 +3082,9 @@
       </c>
       <c r="H121" s="2"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="4">
-        <v>38718</v>
+        <v>38687</v>
       </c>
       <c r="B122" s="4">
         <v>38749</v>
@@ -3014,9 +3103,9 @@
       </c>
       <c r="H122" s="2"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>38749</v>
+        <v>38718</v>
       </c>
       <c r="B123" s="4">
         <v>38777</v>
@@ -3035,9 +3124,9 @@
       </c>
       <c r="H123" s="2"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="4">
-        <v>38777</v>
+        <v>38749</v>
       </c>
       <c r="B124" s="4">
         <v>38808</v>
@@ -3056,9 +3145,9 @@
       </c>
       <c r="H124" s="2"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="4">
-        <v>38808</v>
+        <v>38777</v>
       </c>
       <c r="B125" s="4">
         <v>38838</v>
@@ -3077,9 +3166,9 @@
       </c>
       <c r="H125" s="2"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="4">
-        <v>38838</v>
+        <v>38808</v>
       </c>
       <c r="B126" s="4">
         <v>38869</v>
@@ -3098,9 +3187,9 @@
       </c>
       <c r="H126" s="2"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="4">
-        <v>38869</v>
+        <v>38838</v>
       </c>
       <c r="B127" s="4">
         <v>38899</v>
@@ -3119,9 +3208,9 @@
       </c>
       <c r="H127" s="2"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="4">
-        <v>38899</v>
+        <v>38869</v>
       </c>
       <c r="B128" s="4">
         <v>38930</v>
@@ -3140,9 +3229,9 @@
       </c>
       <c r="H128" s="2"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="4">
-        <v>38930</v>
+        <v>38899</v>
       </c>
       <c r="B129" s="4">
         <v>38961</v>
@@ -3161,9 +3250,9 @@
       </c>
       <c r="H129" s="2"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="4">
-        <v>38961</v>
+        <v>38930</v>
       </c>
       <c r="B130" s="4">
         <v>38991</v>
@@ -3182,9 +3271,9 @@
       </c>
       <c r="H130" s="2"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="4">
-        <v>38991</v>
+        <v>38961</v>
       </c>
       <c r="B131" s="4">
         <v>39022</v>
@@ -3203,9 +3292,9 @@
       </c>
       <c r="H131" s="2"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="4">
-        <v>39022</v>
+        <v>38991</v>
       </c>
       <c r="B132" s="4">
         <v>39052</v>
@@ -3224,9 +3313,9 @@
       </c>
       <c r="H132" s="2"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="4">
-        <v>39052</v>
+        <v>39022</v>
       </c>
       <c r="B133" s="4">
         <v>39083</v>
@@ -3245,9 +3334,9 @@
       </c>
       <c r="H133" s="2"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>39083</v>
+        <v>39052</v>
       </c>
       <c r="B134" s="4">
         <v>39114</v>
@@ -3266,9 +3355,9 @@
       </c>
       <c r="H134" s="2"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="4">
-        <v>39114</v>
+        <v>39083</v>
       </c>
       <c r="B135" s="4">
         <v>39142</v>
@@ -3287,9 +3376,9 @@
       </c>
       <c r="H135" s="2"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="4">
-        <v>39142</v>
+        <v>39114</v>
       </c>
       <c r="B136" s="4">
         <v>39173</v>
@@ -3308,9 +3397,9 @@
       </c>
       <c r="H136" s="2"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="4">
-        <v>39173</v>
+        <v>39142</v>
       </c>
       <c r="B137" s="4">
         <v>39203</v>
@@ -3329,9 +3418,9 @@
       </c>
       <c r="H137" s="2"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="4">
-        <v>39203</v>
+        <v>39173</v>
       </c>
       <c r="B138" s="4">
         <v>39234</v>
@@ -3350,9 +3439,9 @@
       </c>
       <c r="H138" s="2"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="4">
-        <v>39234</v>
+        <v>39203</v>
       </c>
       <c r="B139" s="4">
         <v>39264</v>
@@ -3371,9 +3460,9 @@
       </c>
       <c r="H139" s="2"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="4">
-        <v>39264</v>
+        <v>39234</v>
       </c>
       <c r="B140" s="4">
         <v>39295</v>
@@ -3392,9 +3481,9 @@
       </c>
       <c r="H140" s="2"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="4">
-        <v>39295</v>
+        <v>39264</v>
       </c>
       <c r="B141" s="4">
         <v>39326</v>
@@ -3413,9 +3502,9 @@
       </c>
       <c r="H141" s="2"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="4">
-        <v>39326</v>
+        <v>39295</v>
       </c>
       <c r="B142" s="4">
         <v>39356</v>
@@ -3434,9 +3523,9 @@
       </c>
       <c r="H142" s="2"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="4">
-        <v>39356</v>
+        <v>39326</v>
       </c>
       <c r="B143" s="4">
         <v>39387</v>
@@ -3455,9 +3544,9 @@
       </c>
       <c r="H143" s="2"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="4">
-        <v>39387</v>
+        <v>39356</v>
       </c>
       <c r="B144" s="4">
         <v>39417</v>
@@ -3476,9 +3565,9 @@
       </c>
       <c r="H144" s="2"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>39417</v>
+        <v>39387</v>
       </c>
       <c r="B145" s="4">
         <v>39448</v>
@@ -3497,9 +3586,9 @@
       </c>
       <c r="H145" s="2"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="4">
-        <v>39448</v>
+        <v>39417</v>
       </c>
       <c r="B146" s="4">
         <v>39479</v>
@@ -3518,9 +3607,9 @@
       </c>
       <c r="H146" s="2"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="4">
-        <v>39479</v>
+        <v>39448</v>
       </c>
       <c r="B147" s="4">
         <v>39508</v>
@@ -3539,9 +3628,9 @@
       </c>
       <c r="H147" s="2"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="4">
-        <v>39508</v>
+        <v>39479</v>
       </c>
       <c r="B148" s="4">
         <v>39539</v>
@@ -3560,9 +3649,9 @@
       </c>
       <c r="H148" s="2"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="4">
-        <v>39539</v>
+        <v>39508</v>
       </c>
       <c r="B149" s="4">
         <v>39569</v>
@@ -3581,9 +3670,9 @@
       </c>
       <c r="H149" s="2"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="4">
-        <v>39569</v>
+        <v>39539</v>
       </c>
       <c r="B150" s="4">
         <v>39600</v>
@@ -3602,9 +3691,9 @@
       </c>
       <c r="H150" s="2"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="4">
-        <v>39600</v>
+        <v>39569</v>
       </c>
       <c r="B151" s="4">
         <v>39630</v>
@@ -3623,9 +3712,9 @@
       </c>
       <c r="H151" s="2"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="4">
-        <v>39630</v>
+        <v>39600</v>
       </c>
       <c r="B152" s="4">
         <v>39661</v>
@@ -3644,9 +3733,9 @@
       </c>
       <c r="H152" s="2"/>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="4">
-        <v>39661</v>
+        <v>39630</v>
       </c>
       <c r="B153" s="4">
         <v>39692</v>
@@ -3665,9 +3754,9 @@
       </c>
       <c r="H153" s="2"/>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="4">
-        <v>39692</v>
+        <v>39661</v>
       </c>
       <c r="B154" s="4">
         <v>39722</v>
@@ -3686,9 +3775,9 @@
       </c>
       <c r="H154" s="2"/>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="4">
-        <v>39722</v>
+        <v>39692</v>
       </c>
       <c r="B155" s="4">
         <v>39753</v>
@@ -3707,9 +3796,9 @@
       </c>
       <c r="H155" s="2"/>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>39753</v>
+        <v>39722</v>
       </c>
       <c r="B156" s="4">
         <v>39783</v>
@@ -3728,9 +3817,9 @@
       </c>
       <c r="H156" s="2"/>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="4">
-        <v>39783</v>
+        <v>39753</v>
       </c>
       <c r="B157" s="4">
         <v>39814</v>
@@ -3749,9 +3838,9 @@
       </c>
       <c r="H157" s="2"/>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="4">
-        <v>39814</v>
+        <v>39783</v>
       </c>
       <c r="B158" s="4">
         <v>39845</v>
@@ -3770,9 +3859,9 @@
       </c>
       <c r="H158" s="2"/>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="4">
-        <v>39845</v>
+        <v>39814</v>
       </c>
       <c r="B159" s="4">
         <v>39873</v>
@@ -3791,9 +3880,9 @@
       </c>
       <c r="H159" s="2"/>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="4">
-        <v>39873</v>
+        <v>39845</v>
       </c>
       <c r="B160" s="4">
         <v>39904</v>
@@ -3812,9 +3901,9 @@
       </c>
       <c r="H160" s="2"/>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="4">
-        <v>39904</v>
+        <v>39873</v>
       </c>
       <c r="B161" s="4">
         <v>39934</v>
@@ -3833,9 +3922,9 @@
       </c>
       <c r="H161" s="2"/>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="4">
-        <v>39934</v>
+        <v>39904</v>
       </c>
       <c r="B162" s="4">
         <v>39965</v>
@@ -3854,9 +3943,9 @@
       </c>
       <c r="H162" s="2"/>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="4">
-        <v>39965</v>
+        <v>39934</v>
       </c>
       <c r="B163" s="4">
         <v>39995</v>
@@ -3875,9 +3964,9 @@
       </c>
       <c r="H163" s="2"/>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="4">
-        <v>39995</v>
+        <v>39965</v>
       </c>
       <c r="B164" s="4">
         <v>40026</v>
@@ -3896,9 +3985,9 @@
       </c>
       <c r="H164" s="2"/>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="4">
-        <v>40026</v>
+        <v>39995</v>
       </c>
       <c r="B165" s="4">
         <v>40057</v>
@@ -3917,9 +4006,9 @@
       </c>
       <c r="H165" s="2"/>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="4">
-        <v>40057</v>
+        <v>40026</v>
       </c>
       <c r="B166" s="4">
         <v>40087</v>
@@ -3938,9 +4027,9 @@
       </c>
       <c r="H166" s="2"/>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>40087</v>
+        <v>40057</v>
       </c>
       <c r="B167" s="4">
         <v>40118</v>
@@ -3959,9 +4048,9 @@
       </c>
       <c r="H167" s="2"/>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="4">
-        <v>40118</v>
+        <v>40087</v>
       </c>
       <c r="B168" s="4">
         <v>40148</v>
@@ -3980,9 +4069,9 @@
       </c>
       <c r="H168" s="2"/>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="4">
-        <v>40148</v>
+        <v>40118</v>
       </c>
       <c r="B169" s="4">
         <v>40179</v>
@@ -4001,9 +4090,9 @@
       </c>
       <c r="H169" s="2"/>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="4">
-        <v>40179</v>
+        <v>40148</v>
       </c>
       <c r="B170" s="4">
         <v>40210</v>
@@ -4022,9 +4111,9 @@
       </c>
       <c r="H170" s="2"/>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="4">
-        <v>40210</v>
+        <v>40179</v>
       </c>
       <c r="B171" s="4">
         <v>40238</v>
@@ -4043,9 +4132,9 @@
       </c>
       <c r="H171" s="2"/>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="4">
-        <v>40238</v>
+        <v>40210</v>
       </c>
       <c r="B172" s="4">
         <v>40269</v>
@@ -4064,9 +4153,9 @@
       </c>
       <c r="H172" s="2"/>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="4">
-        <v>40269</v>
+        <v>40238</v>
       </c>
       <c r="B173" s="4">
         <v>40299</v>
@@ -4085,9 +4174,9 @@
       </c>
       <c r="H173" s="2"/>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="4">
-        <v>40299</v>
+        <v>40269</v>
       </c>
       <c r="B174" s="4">
         <v>40330</v>
@@ -4106,9 +4195,9 @@
       </c>
       <c r="H174" s="2"/>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="4">
-        <v>40330</v>
+        <v>40299</v>
       </c>
       <c r="B175" s="4">
         <v>40360</v>
@@ -4127,9 +4216,9 @@
       </c>
       <c r="H175" s="2"/>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="4">
-        <v>40360</v>
+        <v>40330</v>
       </c>
       <c r="B176" s="4">
         <v>40391</v>
@@ -4148,9 +4237,9 @@
       </c>
       <c r="H176" s="2"/>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="4">
-        <v>40391</v>
+        <v>40360</v>
       </c>
       <c r="B177" s="4">
         <v>40422</v>
@@ -4169,9 +4258,9 @@
       </c>
       <c r="H177" s="2"/>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>40422</v>
+        <v>40391</v>
       </c>
       <c r="B178" s="4">
         <v>40452</v>
@@ -4190,9 +4279,9 @@
       </c>
       <c r="H178" s="2"/>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="4">
-        <v>40452</v>
+        <v>40422</v>
       </c>
       <c r="B179" s="4">
         <v>40483</v>
@@ -4211,9 +4300,9 @@
       </c>
       <c r="H179" s="2"/>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="4">
-        <v>40483</v>
+        <v>40452</v>
       </c>
       <c r="B180" s="4">
         <v>40513</v>
@@ -4232,9 +4321,9 @@
       </c>
       <c r="H180" s="2"/>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="4">
-        <v>40513</v>
+        <v>40483</v>
       </c>
       <c r="B181" s="4">
         <v>40544</v>
@@ -4253,9 +4342,9 @@
       </c>
       <c r="H181" s="2"/>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="4">
-        <v>40544</v>
+        <v>40513</v>
       </c>
       <c r="B182" s="4">
         <v>40575</v>
@@ -4274,9 +4363,9 @@
       </c>
       <c r="H182" s="2"/>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" s="4">
-        <v>40575</v>
+        <v>40544</v>
       </c>
       <c r="B183" s="4">
         <v>40603</v>
@@ -4295,9 +4384,9 @@
       </c>
       <c r="H183" s="2"/>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" s="4">
-        <v>40603</v>
+        <v>40575</v>
       </c>
       <c r="B184" s="4">
         <v>40634</v>
@@ -4316,9 +4405,9 @@
       </c>
       <c r="H184" s="2"/>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" s="4">
-        <v>40634</v>
+        <v>40603</v>
       </c>
       <c r="B185" s="4">
         <v>40664</v>
@@ -4337,9 +4426,9 @@
       </c>
       <c r="H185" s="2"/>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" s="4">
-        <v>40664</v>
+        <v>40634</v>
       </c>
       <c r="B186" s="4">
         <v>40695</v>
@@ -4358,9 +4447,9 @@
       </c>
       <c r="H186" s="2"/>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" s="4">
-        <v>40695</v>
+        <v>40664</v>
       </c>
       <c r="B187" s="4">
         <v>40725</v>
@@ -4379,9 +4468,9 @@
       </c>
       <c r="H187" s="2"/>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="4">
-        <v>40725</v>
+        <v>40695</v>
       </c>
       <c r="B188" s="4">
         <v>40756</v>
@@ -4400,9 +4489,9 @@
       </c>
       <c r="H188" s="2"/>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>40756</v>
+        <v>40725</v>
       </c>
       <c r="B189" s="4">
         <v>40787</v>
@@ -4421,9 +4510,9 @@
       </c>
       <c r="H189" s="2"/>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="4">
-        <v>40787</v>
+        <v>40756</v>
       </c>
       <c r="B190" s="4">
         <v>40817</v>
@@ -4442,9 +4531,9 @@
       </c>
       <c r="H190" s="2"/>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" s="4">
-        <v>40817</v>
+        <v>40787</v>
       </c>
       <c r="B191" s="4">
         <v>40848</v>
@@ -4463,9 +4552,9 @@
       </c>
       <c r="H191" s="2"/>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" s="4">
-        <v>40848</v>
+        <v>40817</v>
       </c>
       <c r="B192" s="4">
         <v>40878</v>
@@ -4484,9 +4573,9 @@
       </c>
       <c r="H192" s="2"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="4">
-        <v>40878</v>
+        <v>40848</v>
       </c>
       <c r="B193" s="4">
         <v>40909</v>
@@ -4505,9 +4594,9 @@
       </c>
       <c r="H193" s="2"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="4">
-        <v>40909</v>
+        <v>40878</v>
       </c>
       <c r="B194" s="4">
         <v>40940</v>
@@ -4526,9 +4615,9 @@
       </c>
       <c r="H194" s="2"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="4">
-        <v>40940</v>
+        <v>40909</v>
       </c>
       <c r="B195" s="4">
         <v>40969</v>
@@ -4547,9 +4636,9 @@
       </c>
       <c r="H195" s="2"/>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="4">
-        <v>40969</v>
+        <v>40940</v>
       </c>
       <c r="B196" s="4">
         <v>41000</v>
@@ -4568,9 +4657,9 @@
       </c>
       <c r="H196" s="2"/>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="4">
-        <v>41000</v>
+        <v>40969</v>
       </c>
       <c r="B197" s="4">
         <v>41038</v>
@@ -4589,9 +4678,9 @@
       </c>
       <c r="H197" s="2"/>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="4">
-        <v>41030</v>
+        <v>41000</v>
       </c>
       <c r="B198" s="4">
         <v>41067</v>
@@ -4610,9 +4699,9 @@
       </c>
       <c r="H198" s="2"/>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="4">
-        <v>41061</v>
+        <v>41030</v>
       </c>
       <c r="B199" s="4">
         <v>41101</v>
@@ -4631,9 +4720,9 @@
       </c>
       <c r="H199" s="2"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>41091</v>
+        <v>41061</v>
       </c>
       <c r="B200" s="4">
         <v>41129</v>
@@ -4652,9 +4741,9 @@
       </c>
       <c r="H200" s="2"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="4">
-        <v>41122</v>
+        <v>41091</v>
       </c>
       <c r="B201" s="4">
         <v>41164</v>
@@ -4673,9 +4762,9 @@
       </c>
       <c r="H201" s="2"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="4">
-        <v>41153</v>
+        <v>41122</v>
       </c>
       <c r="B202" s="4">
         <v>41192</v>
@@ -4694,9 +4783,9 @@
       </c>
       <c r="H202" s="2"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="4">
-        <v>41183</v>
+        <v>41153</v>
       </c>
       <c r="B203" s="4">
         <v>41221</v>
@@ -4715,9 +4804,9 @@
       </c>
       <c r="H203" s="2"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="4">
-        <v>41214</v>
+        <v>41183</v>
       </c>
       <c r="B204" s="4">
         <v>41255</v>
@@ -4736,9 +4825,9 @@
       </c>
       <c r="H204" s="2"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="4">
-        <v>41244</v>
+        <v>41214</v>
       </c>
       <c r="B205" s="4">
         <v>41284</v>
@@ -4757,9 +4846,9 @@
       </c>
       <c r="H205" s="2"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="4">
-        <v>41275</v>
+        <v>41244</v>
       </c>
       <c r="B206" s="4">
         <v>41318</v>
@@ -4778,9 +4867,9 @@
       </c>
       <c r="H206" s="2"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="4">
-        <v>41306</v>
+        <v>41275</v>
       </c>
       <c r="B207" s="4">
         <v>41346</v>
@@ -4799,9 +4888,9 @@
       </c>
       <c r="H207" s="2"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="4">
-        <v>41334</v>
+        <v>41306</v>
       </c>
       <c r="B208" s="4">
         <v>41374</v>
@@ -4820,9 +4909,9 @@
       </c>
       <c r="H208" s="2"/>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="4">
-        <v>41365</v>
+        <v>41334</v>
       </c>
       <c r="B209" s="4">
         <v>41402</v>
@@ -4841,9 +4930,9 @@
       </c>
       <c r="H209" s="2"/>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="4">
-        <v>41395</v>
+        <v>41365</v>
       </c>
       <c r="B210" s="4">
         <v>41437</v>
@@ -4862,9 +4951,9 @@
       </c>
       <c r="H210" s="2"/>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>41426</v>
+        <v>41395</v>
       </c>
       <c r="B211" s="4">
         <v>41465</v>
@@ -4883,9 +4972,9 @@
       </c>
       <c r="H211" s="2"/>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" s="4">
-        <v>41456</v>
+        <v>41426</v>
       </c>
       <c r="B212" s="4">
         <v>41493</v>
@@ -4904,9 +4993,9 @@
       </c>
       <c r="H212" s="2"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="4">
-        <v>41487</v>
+        <v>41456</v>
       </c>
       <c r="B213" s="4">
         <v>41528</v>
@@ -4925,9 +5014,9 @@
       </c>
       <c r="H213" s="2"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="4">
-        <v>41518</v>
+        <v>41487</v>
       </c>
       <c r="B214" s="4">
         <v>41556</v>
@@ -4946,9 +5035,9 @@
       </c>
       <c r="H214" s="2"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="4">
-        <v>41548</v>
+        <v>41518</v>
       </c>
       <c r="B215" s="4">
         <v>41591</v>
@@ -4967,9 +5056,9 @@
       </c>
       <c r="H215" s="2"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="4">
-        <v>41579</v>
+        <v>41548</v>
       </c>
       <c r="B216" s="4">
         <v>41619</v>
@@ -4988,9 +5077,9 @@
       </c>
       <c r="H216" s="2"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="4">
-        <v>41609</v>
+        <v>41579</v>
       </c>
       <c r="B217" s="4">
         <v>41647</v>
@@ -5009,9 +5098,9 @@
       </c>
       <c r="H217" s="2"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="4">
-        <v>41640</v>
+        <v>41609</v>
       </c>
       <c r="B218" s="4">
         <v>41682</v>
@@ -5030,9 +5119,9 @@
       </c>
       <c r="H218" s="2"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="4">
-        <v>41671</v>
+        <v>41640</v>
       </c>
       <c r="B219" s="4">
         <v>41710</v>
@@ -5051,9 +5140,9 @@
       </c>
       <c r="H219" s="2"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="4">
-        <v>41699</v>
+        <v>41671</v>
       </c>
       <c r="B220" s="4">
         <v>41738</v>
@@ -5072,9 +5161,9 @@
       </c>
       <c r="H220" s="2"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="4">
-        <v>41730</v>
+        <v>41699</v>
       </c>
       <c r="B221" s="4">
         <v>41767</v>
@@ -5093,9 +5182,9 @@
       </c>
       <c r="H221" s="2"/>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>41760</v>
+        <v>41730</v>
       </c>
       <c r="B222" s="4">
         <v>41801</v>
@@ -5114,9 +5203,9 @@
       </c>
       <c r="H222" s="2"/>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" s="4">
-        <v>41791</v>
+        <v>41760</v>
       </c>
       <c r="B223" s="4">
         <v>41829</v>
@@ -5135,9 +5224,9 @@
       </c>
       <c r="H223" s="2"/>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="4">
-        <v>41821</v>
+        <v>41791</v>
       </c>
       <c r="B224" s="4">
         <v>41864</v>
@@ -5156,9 +5245,9 @@
       </c>
       <c r="H224" s="2"/>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="4">
-        <v>41852</v>
+        <v>41821</v>
       </c>
       <c r="B225" s="4">
         <v>41893</v>
@@ -5177,9 +5266,9 @@
       </c>
       <c r="H225" s="2"/>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="4">
-        <v>41883</v>
+        <v>41852</v>
       </c>
       <c r="B226" s="4">
         <v>41926</v>
@@ -5198,9 +5287,9 @@
       </c>
       <c r="H226" s="2"/>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" s="4">
-        <v>41913</v>
+        <v>41883</v>
       </c>
       <c r="B227" s="4">
         <v>41955</v>
@@ -5219,9 +5308,9 @@
       </c>
       <c r="H227" s="2"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="4">
-        <v>41944</v>
+        <v>41913</v>
       </c>
       <c r="B228" s="4">
         <v>41983</v>
@@ -5240,9 +5329,9 @@
       </c>
       <c r="H228" s="2"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="4">
-        <v>41974</v>
+        <v>41944</v>
       </c>
       <c r="B229" s="4">
         <v>42018</v>
@@ -5261,9 +5350,9 @@
       </c>
       <c r="H229" s="2"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="4">
-        <v>42005</v>
+        <v>41974</v>
       </c>
       <c r="B230" s="4">
         <v>42051</v>
@@ -5282,9 +5371,9 @@
       </c>
       <c r="H230" s="2"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="4">
-        <v>42036</v>
+        <v>42005</v>
       </c>
       <c r="B231" s="4">
         <v>42074</v>
@@ -5303,9 +5392,9 @@
       </c>
       <c r="H231" s="2"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="4">
-        <v>42064</v>
+        <v>42036</v>
       </c>
       <c r="B232" s="4">
         <v>42102</v>
@@ -5324,9 +5413,9 @@
       </c>
       <c r="H232" s="2"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>42095</v>
+        <v>42064</v>
       </c>
       <c r="B233" s="4">
         <v>42138</v>
@@ -5345,9 +5434,9 @@
       </c>
       <c r="H233" s="2"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="4">
-        <v>42125</v>
+        <v>42095</v>
       </c>
       <c r="B234" s="4">
         <v>42165</v>
@@ -5366,9 +5455,9 @@
       </c>
       <c r="H234" s="2"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="4">
-        <v>42156</v>
+        <v>42125</v>
       </c>
       <c r="B235" s="4">
         <v>42193</v>
@@ -5387,9 +5476,9 @@
       </c>
       <c r="H235" s="2"/>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="4">
-        <v>42186</v>
+        <v>42156</v>
       </c>
       <c r="B236" s="4">
         <v>42228</v>
@@ -5408,9 +5497,9 @@
       </c>
       <c r="H236" s="2"/>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" s="4">
-        <v>42217</v>
+        <v>42186</v>
       </c>
       <c r="B237" s="4">
         <v>42257</v>
@@ -5429,9 +5518,9 @@
       </c>
       <c r="H237" s="2"/>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" s="4">
-        <v>42248</v>
+        <v>42217</v>
       </c>
       <c r="B238" s="4">
         <v>42291</v>
@@ -5450,9 +5539,9 @@
       </c>
       <c r="H238" s="2"/>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="4">
-        <v>42278</v>
+        <v>42248</v>
       </c>
       <c r="B239" s="4">
         <v>42319</v>
@@ -5471,9 +5560,9 @@
       </c>
       <c r="H239" s="2"/>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" s="4">
-        <v>42309</v>
+        <v>42278</v>
       </c>
       <c r="B240" s="4">
         <v>42347</v>
@@ -5492,9 +5581,9 @@
       </c>
       <c r="H240" s="2"/>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="4">
-        <v>42339</v>
+        <v>42309</v>
       </c>
       <c r="B241" s="4">
         <v>42382</v>
@@ -5513,9 +5602,9 @@
       </c>
       <c r="H241" s="2"/>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" s="4">
-        <v>42370</v>
+        <v>42339</v>
       </c>
       <c r="B242" s="4">
         <v>42415</v>
@@ -5534,9 +5623,9 @@
       </c>
       <c r="H242" s="2"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="4">
-        <v>42401</v>
+        <v>42370</v>
       </c>
       <c r="B243" s="4">
         <v>42438</v>
@@ -5555,9 +5644,9 @@
       </c>
       <c r="H243" s="2"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>42430</v>
+        <v>42401</v>
       </c>
       <c r="B244" s="4">
         <v>42478</v>
@@ -5576,9 +5665,9 @@
       </c>
       <c r="H244" s="2"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="4">
-        <v>42461</v>
+        <v>42430</v>
       </c>
       <c r="B245" s="4">
         <v>42502</v>
@@ -5597,9 +5686,9 @@
       </c>
       <c r="H245" s="2"/>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" s="4">
-        <v>42491</v>
+        <v>42461</v>
       </c>
       <c r="B246" s="4">
         <v>42529</v>
@@ -5618,9 +5707,9 @@
       </c>
       <c r="H246" s="2"/>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" s="4">
-        <v>42522</v>
+        <v>42491</v>
       </c>
       <c r="B247" s="4">
         <v>42564</v>
@@ -5639,9 +5728,9 @@
       </c>
       <c r="H247" s="2"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" s="4">
-        <v>42552</v>
+        <v>42522</v>
       </c>
       <c r="B248" s="4">
         <v>42592</v>
@@ -5660,9 +5749,9 @@
       </c>
       <c r="H248" s="2"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" s="4">
-        <v>42583</v>
+        <v>42552</v>
       </c>
       <c r="B249" s="4">
         <v>42621</v>
@@ -5681,9 +5770,9 @@
       </c>
       <c r="H249" s="2"/>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" s="4">
-        <v>42614</v>
+        <v>42583</v>
       </c>
       <c r="B250" s="4">
         <v>42655</v>
@@ -5702,9 +5791,9 @@
       </c>
       <c r="H250" s="2"/>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" s="4">
-        <v>42644</v>
+        <v>42614</v>
       </c>
       <c r="B251" s="4">
         <v>42684</v>
@@ -5723,9 +5812,9 @@
       </c>
       <c r="H251" s="2"/>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="4">
-        <v>42675</v>
+        <v>42644</v>
       </c>
       <c r="B252" s="4">
         <v>42718</v>
@@ -5744,9 +5833,9 @@
       </c>
       <c r="H252" s="2"/>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" s="4">
-        <v>42705</v>
+        <v>42675</v>
       </c>
       <c r="B253" s="4">
         <v>42747</v>
@@ -5765,9 +5854,9 @@
       </c>
       <c r="H253" s="2"/>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" s="4">
-        <v>42736</v>
+        <v>42705</v>
       </c>
       <c r="B254" s="4">
         <v>42774</v>
@@ -5786,9 +5875,9 @@
       </c>
       <c r="H254" s="2"/>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>42767</v>
+        <v>42736</v>
       </c>
       <c r="B255" s="4">
         <v>42803</v>
@@ -5807,9 +5896,9 @@
       </c>
       <c r="H255" s="2"/>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" s="4">
-        <v>42795</v>
+        <v>42767</v>
       </c>
       <c r="B256" s="4">
         <v>42836</v>
@@ -5828,9 +5917,9 @@
       </c>
       <c r="H256" s="2"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257" s="4">
-        <v>42826</v>
+        <v>42795</v>
       </c>
       <c r="B257" s="4">
         <v>42871</v>
@@ -5849,9 +5938,9 @@
       </c>
       <c r="H257" s="2"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" s="4">
-        <v>42856</v>
+        <v>42826</v>
       </c>
       <c r="B258" s="4">
         <v>42899</v>
@@ -5870,9 +5959,9 @@
       </c>
       <c r="H258" s="2"/>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259" s="4">
-        <v>42887</v>
+        <v>42856</v>
       </c>
       <c r="B259" s="4">
         <v>42928</v>
@@ -5891,9 +5980,9 @@
       </c>
       <c r="H259" s="2"/>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" s="4">
-        <v>42917</v>
+        <v>42887</v>
       </c>
       <c r="B260" s="4">
         <v>42956</v>
@@ -5912,9 +6001,9 @@
       </c>
       <c r="H260" s="2"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" s="4">
-        <v>42948</v>
+        <v>42917</v>
       </c>
       <c r="B261" s="4">
         <v>42990</v>
@@ -5933,9 +6022,9 @@
       </c>
       <c r="H261" s="2"/>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" s="4">
-        <v>42979</v>
+        <v>42948</v>
       </c>
       <c r="B262" s="4">
         <v>43026</v>
@@ -5954,9 +6043,9 @@
       </c>
       <c r="H262" s="2"/>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263" s="4">
-        <v>43009</v>
+        <v>42979</v>
       </c>
       <c r="B263" s="4">
         <v>43047</v>
@@ -5975,9 +6064,9 @@
       </c>
       <c r="H263" s="2"/>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" s="4">
-        <v>43040</v>
+        <v>43009</v>
       </c>
       <c r="B264" s="4">
         <v>43082</v>
@@ -5996,9 +6085,9 @@
       </c>
       <c r="H264" s="2"/>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A265" s="4">
-        <v>43070</v>
+        <v>43040</v>
       </c>
       <c r="B265" s="4">
         <v>43110</v>
@@ -6017,9 +6106,9 @@
       </c>
       <c r="H265" s="2"/>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>43101</v>
+        <v>43070</v>
       </c>
       <c r="B266" s="4">
         <v>43144</v>
@@ -6038,9 +6127,9 @@
       </c>
       <c r="H266" s="2"/>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A267" s="4">
-        <v>43132</v>
+        <v>43101</v>
       </c>
       <c r="B267" s="4">
         <v>43173</v>
@@ -6059,9 +6148,9 @@
       </c>
       <c r="H267" s="2"/>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A268" s="4">
-        <v>43160</v>
+        <v>43132</v>
       </c>
       <c r="B268" s="4">
         <v>43201</v>
@@ -6080,9 +6169,9 @@
       </c>
       <c r="H268" s="2"/>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A269" s="4">
-        <v>43191</v>
+        <v>43160</v>
       </c>
       <c r="B269" s="4">
         <v>43230</v>
@@ -6101,9 +6190,9 @@
       </c>
       <c r="H269" s="2"/>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A270" s="4">
-        <v>43221</v>
+        <v>43191</v>
       </c>
       <c r="B270" s="4">
         <v>43263</v>
@@ -6122,9 +6211,9 @@
       </c>
       <c r="H270" s="2"/>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A271" s="4">
-        <v>43252</v>
+        <v>43221</v>
       </c>
       <c r="B271" s="4">
         <v>43292</v>
@@ -6143,9 +6232,9 @@
       </c>
       <c r="H271" s="2"/>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A272" s="4">
-        <v>43282</v>
+        <v>43252</v>
       </c>
       <c r="B272" s="4">
         <v>43321</v>
@@ -6164,9 +6253,9 @@
       </c>
       <c r="H272" s="2"/>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A273" s="4">
-        <v>43313</v>
+        <v>43282</v>
       </c>
       <c r="B273" s="4">
         <v>43355</v>
@@ -6185,9 +6274,9 @@
       </c>
       <c r="H273" s="2"/>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A274" s="4">
-        <v>43344</v>
+        <v>43313</v>
       </c>
       <c r="B274" s="4">
         <v>43390</v>
@@ -6206,9 +6295,9 @@
       </c>
       <c r="H274" s="2"/>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A275" s="4">
-        <v>43374</v>
+        <v>43344</v>
       </c>
       <c r="B275" s="4">
         <v>43417</v>
@@ -6227,9 +6316,9 @@
       </c>
       <c r="H275" s="2"/>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A276" s="4">
-        <v>43405</v>
+        <v>43374</v>
       </c>
       <c r="B276" s="4">
         <v>43446</v>
@@ -6248,9 +6337,9 @@
       </c>
       <c r="H276" s="2"/>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>43435</v>
+        <v>43405</v>
       </c>
       <c r="B277" s="4">
         <v>43475</v>
@@ -6269,9 +6358,9 @@
       </c>
       <c r="H277" s="2"/>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A278" s="4">
-        <v>43466</v>
+        <v>43435</v>
       </c>
       <c r="B278" s="4">
         <v>43510</v>
@@ -6290,9 +6379,9 @@
       </c>
       <c r="H278" s="2"/>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A279" s="4">
-        <v>43497</v>
+        <v>43466</v>
       </c>
       <c r="B279" s="4">
         <v>43537</v>
@@ -6311,9 +6400,9 @@
       </c>
       <c r="H279" s="2"/>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A280" s="4">
-        <v>43525</v>
+        <v>43497</v>
       </c>
       <c r="B280" s="4">
         <v>43566</v>
@@ -6332,9 +6421,9 @@
       </c>
       <c r="H280" s="2"/>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A281" s="4">
-        <v>43556</v>
+        <v>43525</v>
       </c>
       <c r="B281" s="4">
         <v>43594</v>
@@ -6353,9 +6442,9 @@
       </c>
       <c r="H281" s="2"/>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A282" s="4">
-        <v>43586</v>
+        <v>43556</v>
       </c>
       <c r="B282" s="4">
         <v>43628</v>
@@ -6374,9 +6463,9 @@
       </c>
       <c r="H282" s="2"/>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A283" s="4">
-        <v>43617</v>
+        <v>43586</v>
       </c>
       <c r="B283" s="4">
         <v>43657</v>
@@ -6395,9 +6484,9 @@
       </c>
       <c r="H283" s="2"/>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A284" s="4">
-        <v>43647</v>
+        <v>43617</v>
       </c>
       <c r="B284" s="4">
         <v>43690</v>
@@ -6416,9 +6505,9 @@
       </c>
       <c r="H284" s="2"/>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A285" s="4">
-        <v>43678</v>
+        <v>43647</v>
       </c>
       <c r="B285" s="4">
         <v>43727</v>
@@ -6437,9 +6526,9 @@
       </c>
       <c r="H285" s="2"/>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A286" s="4">
-        <v>43709</v>
+        <v>43678</v>
       </c>
       <c r="B286" s="4">
         <v>43753</v>
@@ -6458,9 +6547,9 @@
       </c>
       <c r="H286" s="2"/>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A287" s="4">
-        <v>43739</v>
+        <v>43709</v>
       </c>
       <c r="B287" s="4">
         <v>43782</v>
@@ -6479,9 +6568,9 @@
       </c>
       <c r="H287" s="2"/>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>43770</v>
+        <v>43739</v>
       </c>
       <c r="B288" s="4">
         <v>43810</v>
@@ -6500,9 +6589,9 @@
       </c>
       <c r="H288" s="2"/>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A289" s="4">
-        <v>43800</v>
+        <v>43770</v>
       </c>
       <c r="B289" s="4">
         <v>43846</v>
@@ -6521,9 +6610,9 @@
       </c>
       <c r="H289" s="2"/>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A290" s="4">
-        <v>43831</v>
+        <v>43800</v>
       </c>
       <c r="B290" s="4">
         <v>43875</v>
@@ -6542,9 +6631,9 @@
       </c>
       <c r="H290" s="2"/>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A291" s="4">
-        <v>43862</v>
+        <v>43831</v>
       </c>
       <c r="B291" s="4">
         <v>43907</v>
@@ -6563,9 +6652,9 @@
       </c>
       <c r="H291" s="2"/>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A292" s="4">
-        <v>43891</v>
+        <v>43862</v>
       </c>
       <c r="B292" s="4">
         <v>43931</v>
@@ -6584,9 +6673,9 @@
       </c>
       <c r="H292" s="2"/>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A293" s="4">
-        <v>43922</v>
+        <v>43891</v>
       </c>
       <c r="B293" s="4">
         <v>43964</v>
@@ -6605,9 +6694,9 @@
       </c>
       <c r="H293" s="2"/>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A294" s="4">
-        <v>43952</v>
+        <v>43922</v>
       </c>
       <c r="B294" s="4">
         <v>43992</v>
@@ -6626,9 +6715,9 @@
       </c>
       <c r="H294" s="2"/>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A295" s="4">
-        <v>43983</v>
+        <v>43952</v>
       </c>
       <c r="B295" s="4">
         <v>44027</v>
@@ -6647,9 +6736,9 @@
       </c>
       <c r="H295" s="2"/>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A296" s="4">
-        <v>44013</v>
+        <v>43983</v>
       </c>
       <c r="B296" s="4">
         <v>44056</v>
@@ -6668,9 +6757,9 @@
       </c>
       <c r="H296" s="2"/>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A297" s="4">
-        <v>44044</v>
+        <v>44013</v>
       </c>
       <c r="B297" s="4">
         <v>44085</v>
@@ -6689,9 +6778,9 @@
       </c>
       <c r="H297" s="2"/>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A298" s="4">
-        <v>44075</v>
+        <v>44044</v>
       </c>
       <c r="B298" s="4">
         <v>44119</v>
@@ -6710,9 +6799,9 @@
       </c>
       <c r="H298" s="2"/>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>44105</v>
+        <v>44075</v>
       </c>
       <c r="B299" s="4">
         <v>44148</v>
@@ -6731,9 +6820,9 @@
       </c>
       <c r="H299" s="2"/>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A300" s="4">
-        <v>44136</v>
+        <v>44105</v>
       </c>
       <c r="B300" s="4">
         <v>44180</v>
@@ -6752,9 +6841,9 @@
       </c>
       <c r="H300" s="2"/>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A301" s="4">
-        <v>44166</v>
+        <v>44136</v>
       </c>
       <c r="B301" s="4">
         <v>44209</v>
@@ -6773,9 +6862,9 @@
       </c>
       <c r="H301" s="2"/>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A302" s="4">
-        <v>44197</v>
+        <v>44166</v>
       </c>
       <c r="B302" s="4">
         <v>44244</v>
@@ -6794,9 +6883,9 @@
       </c>
       <c r="H302" s="2"/>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A303" s="4">
-        <v>44228</v>
+        <v>44197</v>
       </c>
       <c r="B303" s="4">
         <v>44273</v>
@@ -6815,9 +6904,9 @@
       </c>
       <c r="H303" s="2"/>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A304" s="4">
-        <v>44256</v>
+        <v>44228</v>
       </c>
       <c r="B304" s="4">
         <v>44299</v>
@@ -6836,9 +6925,9 @@
       </c>
       <c r="H304" s="2"/>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A305" s="4">
-        <v>44287</v>
+        <v>44256</v>
       </c>
       <c r="B305" s="4">
         <v>44329</v>
@@ -6857,9 +6946,9 @@
       </c>
       <c r="H305" s="2"/>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A306" s="4">
-        <v>44317</v>
+        <v>44287</v>
       </c>
       <c r="B306" s="4">
         <v>44362</v>
@@ -6878,9 +6967,9 @@
       </c>
       <c r="H306" s="2"/>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A307" s="4">
-        <v>44348</v>
+        <v>44317</v>
       </c>
       <c r="B307" s="4">
         <v>44390</v>
@@ -6899,9 +6988,9 @@
       </c>
       <c r="H307" s="2"/>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A308" s="4">
-        <v>44378</v>
+        <v>44348</v>
       </c>
       <c r="B308" s="4">
         <v>44420</v>
@@ -6920,9 +7009,9 @@
       </c>
       <c r="H308" s="2"/>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A309" s="4">
-        <v>44409</v>
+        <v>44378</v>
       </c>
       <c r="B309" s="4">
         <v>44453</v>
@@ -6941,9 +7030,9 @@
       </c>
       <c r="H309" s="2"/>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>44440</v>
+        <v>44409</v>
       </c>
       <c r="B310" s="4">
         <v>44482</v>
@@ -6962,9 +7051,9 @@
       </c>
       <c r="H310" s="2"/>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A311" s="4">
-        <v>44470</v>
+        <v>44440</v>
       </c>
       <c r="B311" s="4">
         <v>44511</v>
@@ -6983,9 +7072,9 @@
       </c>
       <c r="H311" s="2"/>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A312" s="4">
-        <v>44501</v>
+        <v>44470</v>
       </c>
       <c r="B312" s="4">
         <v>44545</v>
@@ -7004,9 +7093,9 @@
       </c>
       <c r="H312" s="2"/>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A313" s="4">
-        <v>44531</v>
+        <v>44501</v>
       </c>
       <c r="B313" s="4">
         <v>44573</v>
@@ -7025,9 +7114,9 @@
       </c>
       <c r="H313" s="2"/>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A314" s="4">
-        <v>44562</v>
+        <v>44531</v>
       </c>
       <c r="B314" s="4">
         <v>44609</v>
@@ -7046,9 +7135,9 @@
       </c>
       <c r="H314" s="2"/>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A315" s="4">
-        <v>44593</v>
+        <v>44562</v>
       </c>
       <c r="B315" s="4">
         <v>44637</v>
@@ -7067,9 +7156,9 @@
       </c>
       <c r="H315" s="2"/>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A316" s="4">
-        <v>44621</v>
+        <v>44593</v>
       </c>
       <c r="B316" s="4">
         <v>44663</v>
@@ -7088,9 +7177,9 @@
       </c>
       <c r="H316" s="2"/>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A317" s="4">
-        <v>44652</v>
+        <v>44621</v>
       </c>
       <c r="B317" s="4">
         <v>44693</v>
@@ -7109,9 +7198,9 @@
       </c>
       <c r="H317" s="2"/>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A318" s="4">
-        <v>44682</v>
+        <v>44652</v>
       </c>
       <c r="B318" s="4">
         <v>44727</v>
@@ -7130,9 +7219,9 @@
       </c>
       <c r="H318" s="2"/>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A319" s="4">
-        <v>44713</v>
+        <v>44682</v>
       </c>
       <c r="B319" s="4">
         <v>44754</v>
@@ -7151,9 +7240,9 @@
       </c>
       <c r="H319" s="2"/>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A320" s="4">
-        <v>44743</v>
+        <v>44713</v>
       </c>
       <c r="B320" s="4">
         <v>44784</v>
@@ -7172,9 +7261,9 @@
       </c>
       <c r="H320" s="2"/>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>44774</v>
+        <v>44743</v>
       </c>
       <c r="B321" s="4">
         <v>44820</v>
@@ -7193,9 +7282,9 @@
       </c>
       <c r="H321" s="2"/>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A322" s="4">
-        <v>44805</v>
+        <v>44774</v>
       </c>
       <c r="B322" s="4">
         <v>44852</v>
@@ -7214,9 +7303,9 @@
       </c>
       <c r="H322" s="2"/>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A323" s="4">
-        <v>44835</v>
+        <v>44805</v>
       </c>
       <c r="B323" s="4">
         <v>44880</v>
@@ -7235,9 +7324,9 @@
       </c>
       <c r="H323" s="2"/>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A324" s="4">
-        <v>44866</v>
+        <v>44835</v>
       </c>
       <c r="B324" s="4">
         <v>44908</v>
@@ -7256,9 +7345,9 @@
       </c>
       <c r="H324" s="2"/>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A325" s="4">
-        <v>44896</v>
+        <v>44866</v>
       </c>
       <c r="B325" s="4">
         <v>44943</v>
@@ -7277,9 +7366,9 @@
       </c>
       <c r="H325" s="2"/>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A326" s="4">
-        <v>44927</v>
+        <v>44896</v>
       </c>
       <c r="B326" s="4">
         <v>44971</v>
@@ -7298,9 +7387,9 @@
       </c>
       <c r="H326" s="2"/>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A327" s="4">
-        <v>44958</v>
+        <v>44927</v>
       </c>
       <c r="B327" s="4">
         <v>45000</v>
@@ -7319,9 +7408,9 @@
       </c>
       <c r="H327" s="2"/>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A328" s="4">
-        <v>44986</v>
+        <v>44958</v>
       </c>
       <c r="B328" s="4">
         <v>45030</v>
@@ -7343,9 +7432,9 @@
       </c>
       <c r="H328" s="2"/>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A329" s="4">
-        <v>45017</v>
+        <v>44986</v>
       </c>
       <c r="B329" s="4">
         <v>45058</v>
@@ -7367,9 +7456,9 @@
       </c>
       <c r="H329" s="2"/>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A330" s="4">
-        <v>45047</v>
+        <v>45017</v>
       </c>
       <c r="B330" s="4">
         <v>45091</v>
@@ -7391,9 +7480,9 @@
       </c>
       <c r="H330" s="2"/>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A331" s="4">
-        <v>45078</v>
+        <v>45047</v>
       </c>
       <c r="B331" s="4">
         <v>45121</v>
@@ -7415,9 +7504,9 @@
       </c>
       <c r="H331" s="2"/>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>45108</v>
+        <v>45078</v>
       </c>
       <c r="B332" s="4">
         <v>45149</v>
@@ -7439,9 +7528,9 @@
       </c>
       <c r="H332" s="2"/>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A333" s="4">
-        <v>45139</v>
+        <v>45108</v>
       </c>
       <c r="B333" s="4">
         <v>45182</v>
@@ -7460,9 +7549,9 @@
       </c>
       <c r="H333" s="2"/>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A334" s="4">
-        <v>45170</v>
+        <v>45139</v>
       </c>
       <c r="B334" s="4">
         <v>45216</v>
@@ -7481,9 +7570,9 @@
       </c>
       <c r="H334" s="2"/>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A335" s="4">
-        <v>45200</v>
+        <v>45170</v>
       </c>
       <c r="B335" s="4">
         <v>45244</v>
@@ -7502,9 +7591,9 @@
       </c>
       <c r="H335" s="2"/>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A336" s="4">
-        <v>45231</v>
+        <v>45200</v>
       </c>
       <c r="B336" s="4">
         <v>45273</v>
@@ -7523,9 +7612,9 @@
       </c>
       <c r="H336" s="2"/>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A337" s="4">
-        <v>45261</v>
+        <v>45231</v>
       </c>
       <c r="B337" s="4">
         <v>45308</v>
@@ -7544,9 +7633,9 @@
       </c>
       <c r="H337" s="2"/>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A338" s="4">
-        <v>45292</v>
+        <v>45261</v>
       </c>
       <c r="B338" s="4">
         <v>45338</v>
@@ -7565,9 +7654,9 @@
       </c>
       <c r="H338" s="2"/>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A339" s="4">
-        <v>45323</v>
+        <v>45292</v>
       </c>
       <c r="B339" s="4">
         <v>45366</v>
@@ -7586,9 +7675,9 @@
       </c>
       <c r="H339" s="2"/>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A340" s="4">
-        <v>45352</v>
+        <v>45323</v>
       </c>
       <c r="B340" s="4">
         <v>45398</v>
@@ -7607,9 +7696,9 @@
       </c>
       <c r="H340" s="2"/>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A341" s="4">
-        <v>45383</v>
+        <v>45352</v>
       </c>
       <c r="B341" s="4">
         <v>45428</v>
@@ -7628,9 +7717,9 @@
       </c>
       <c r="H341" s="2"/>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A342" s="4">
-        <v>45413</v>
+        <v>45383</v>
       </c>
       <c r="B342" s="4">
         <v>45457</v>
@@ -7649,9 +7738,9 @@
       </c>
       <c r="H342" s="2"/>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>45444</v>
+        <v>45413</v>
       </c>
       <c r="B343" s="4">
         <v>45488</v>
@@ -7670,9 +7759,9 @@
       </c>
       <c r="H343" s="2"/>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A344" s="4">
-        <v>45474</v>
+        <v>45444</v>
       </c>
       <c r="B344" s="4">
         <v>45517</v>
@@ -7691,9 +7780,9 @@
       </c>
       <c r="H344" s="2"/>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" s="4">
-        <v>45505</v>
+        <v>45474</v>
       </c>
       <c r="B345" s="4">
         <v>45548</v>
@@ -7712,9 +7801,9 @@
       </c>
       <c r="H345" s="2"/>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A346" s="4">
-        <v>45536</v>
+        <v>45505</v>
       </c>
       <c r="B346" s="4">
         <v>45581</v>
@@ -7733,9 +7822,9 @@
       </c>
       <c r="H346" s="2"/>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A347" s="4">
-        <v>45566</v>
+        <v>45536</v>
       </c>
       <c r="B347" s="4">
         <v>45610</v>
@@ -7754,9 +7843,9 @@
       </c>
       <c r="H347" s="2"/>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A348" s="4">
-        <v>45597</v>
+        <v>45566</v>
       </c>
       <c r="B348" s="4">
         <v>45642</v>
@@ -7775,9 +7864,9 @@
       </c>
       <c r="H348" s="2"/>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A349" s="4">
-        <v>45627</v>
+        <v>45597</v>
       </c>
       <c r="B349" s="4">
         <v>45671</v>
@@ -7796,9 +7885,9 @@
       </c>
       <c r="H349" s="2"/>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A350" s="4">
-        <v>45658</v>
+        <v>45627</v>
       </c>
       <c r="B350" s="4">
         <v>45701</v>
@@ -7817,9 +7906,9 @@
       </c>
       <c r="H350" s="2"/>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A351" s="4">
-        <v>45689</v>
+        <v>45658</v>
       </c>
       <c r="B351" s="4">
         <v>45733</v>
@@ -7838,9 +7927,9 @@
       </c>
       <c r="H351" s="2"/>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A352" s="4">
-        <v>45717</v>
+        <v>45689</v>
       </c>
       <c r="B352" s="4">
         <v>45762</v>
@@ -7859,9 +7948,9 @@
       </c>
       <c r="H352" s="2"/>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A353" s="4">
-        <v>45748</v>
+        <v>45717</v>
       </c>
       <c r="B353" s="4">
         <v>45792</v>
@@ -7880,9 +7969,9 @@
       </c>
       <c r="H353" s="2"/>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="B354" s="4">
         <v>45824</v>
@@ -7901,9 +7990,9 @@
       </c>
       <c r="H354" s="2"/>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A355" s="4">
-        <v>45809</v>
+        <v>45778</v>
       </c>
       <c r="B355" s="4">
         <v>45853</v>
@@ -7922,9 +8011,9 @@
       </c>
       <c r="H355" s="2"/>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A356" s="4">
-        <v>45839</v>
+        <v>45809</v>
       </c>
       <c r="B356" s="4">
         <v>45882</v>
@@ -7946,9 +8035,9 @@
       </c>
       <c r="H356" s="2"/>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A357" s="4">
-        <v>45870</v>
+        <v>45839</v>
       </c>
       <c r="B357" s="4">
         <v>45916</v>
@@ -7967,9 +8056,9 @@
       </c>
       <c r="H357" s="2"/>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" s="4">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="B358" s="4">
         <v>45945</v>
@@ -7988,9 +8077,9 @@
       </c>
       <c r="H358" s="2"/>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A359" s="4">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="B359" s="4">
         <v>45973</v>
@@ -8009,9 +8098,9 @@
       </c>
       <c r="H359" s="2"/>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A360" s="4">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="B360" s="4">
         <v>46007</v>
@@ -8030,9 +8119,9 @@
       </c>
       <c r="H360" s="2"/>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A361" s="4">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="B361" s="4">
         <v>46036</v>
@@ -8051,9 +8140,9 @@
       </c>
       <c r="H361" s="2"/>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A362" s="4">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="B362" s="4">
         <v>46066</v>
@@ -8072,9 +8161,9 @@
       </c>
       <c r="H362" s="2"/>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A363" s="4">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="B363" s="4">
         <v>46094</v>
@@ -8093,9 +8182,9 @@
       </c>
       <c r="H363" s="2"/>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A364" s="4">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="B364" s="4">
         <v>46127</v>
@@ -8114,9 +8203,9 @@
       </c>
       <c r="H364" s="2"/>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="B365" s="4">
         <v>46155</v>
@@ -8135,9 +8224,9 @@
       </c>
       <c r="H365" s="2"/>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A366" s="4">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="B366" s="4">
         <v>46189</v>
@@ -8156,9 +8245,9 @@
       </c>
       <c r="H366" s="2"/>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A367" s="4">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="B367" s="4">
         <v>46218</v>
@@ -8169,10 +8258,50 @@
       <c r="D367" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="E367" s="1">
+        <v>9.1999999999999998E-2</v>
+      </c>
       <c r="G367" s="1">
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="H367" s="2"/>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A368" s="4">
+        <v>46174</v>
+      </c>
+      <c r="B368" s="4">
+        <v>46248</v>
+      </c>
+      <c r="C368" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D368" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E368" s="1">
+        <v>9.4E-2</v>
+      </c>
+      <c r="G368" s="1">
+        <v>9.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A369" s="4">
+        <v>46204</v>
+      </c>
+      <c r="B369" s="4">
+        <v>46280</v>
+      </c>
+      <c r="C369" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D369" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G369" s="1">
+        <v>9.4E-2</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G367">
@@ -8180,4 +8309,69 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BC03B8D-839C-F744-A273-B6372FC00F3F}">
+  <dimension ref="B2:G4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="8.83203125" style="11"/>
+    <col min="3" max="3" width="12.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="82.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="11"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B3" s="12">
+        <v>1</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>